--- a/Test_Data.xlsx
+++ b/Test_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annalenaroth/Desktop/Dissertation/Raw_Data_Repos/EduMPI_Usability_Test_Data_2023_24/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annalenaroth/Desktop/Dissertation/Python_Studies/First_Study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA59513A-6BDE-F346-BD8C-8D0E1B792558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19E37C3-B2FB-9D4A-9C58-AFEA4A53FD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="3280" windowWidth="27200" windowHeight="14320" xr2:uid="{871A07A0-ABDB-E142-897D-3D285874B1F7}"/>
+    <workbookView xWindow="1420" yWindow="3400" windowWidth="27200" windowHeight="14320" xr2:uid="{871A07A0-ABDB-E142-897D-3D285874B1F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="248">
   <si>
     <t>Count of program executions</t>
   </si>
@@ -715,9 +715,6 @@
     <t>Distribution across 7 nodes</t>
   </si>
   <si>
-    <t>Distribution is not clear / not obvious</t>
-  </si>
-  <si>
     <t>Confusion about nodes and cores; after extensive discussion, distribution across 7 nodes</t>
   </si>
   <si>
@@ -790,9 +787,6 @@
     <t>Visual representation of cluster, nodes, and processes; better suited for a large number of MPI processes</t>
   </si>
   <si>
-    <t>Distribution of 50 processes across 2 nodes, 25 processes each</t>
-  </si>
-  <si>
     <t>Detailed data; consideration of how many bytes are sent to transfer complete matrices</t>
   </si>
   <si>
@@ -857,6 +851,42 @@
   </si>
   <si>
     <t>both</t>
+  </si>
+  <si>
+    <t>Visualization Phase: Tasks, question, correctness</t>
+  </si>
+  <si>
+    <t>Process distribution</t>
+  </si>
+  <si>
+    <t>Performance metrics and views</t>
+  </si>
+  <si>
+    <t>Color coding</t>
+  </si>
+  <si>
+    <t>interpretation of program behavior</t>
+  </si>
+  <si>
+    <t>correct</t>
+  </si>
+  <si>
+    <t>incorrect</t>
+  </si>
+  <si>
+    <t>correct (limited to p2p vs. coll)</t>
+  </si>
+  <si>
+    <t>correct (after discussion)</t>
+  </si>
+  <si>
+    <t>correct (immediately)</t>
+  </si>
+  <si>
+    <t>Distribution of 50 processes across 2 nodes, 25 processes each (was correct in the setting)</t>
+  </si>
+  <si>
+    <t>correct (after discussion, in 2D view)</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1071,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1088,6 +1118,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1109,95 +1142,122 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="45" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="45" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="45" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="45" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="45" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="45" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="45" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="45" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1533,7 +1593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07D9C53D-D0F9-384B-BA23-9FBDFCD86A62}">
-  <dimension ref="A1:AF28"/>
+  <dimension ref="A1:AJ28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -1555,71 +1615,82 @@
     <col min="18" max="18" width="57.1640625" customWidth="1"/>
     <col min="19" max="19" width="53.5" customWidth="1"/>
     <col min="20" max="20" width="58.83203125" customWidth="1"/>
-    <col min="21" max="22" width="71.1640625" customWidth="1"/>
+    <col min="21" max="21" width="71.1640625" customWidth="1"/>
+    <col min="22" max="22" width="30.5" customWidth="1"/>
     <col min="23" max="23" width="58.83203125" customWidth="1"/>
     <col min="24" max="24" width="116" customWidth="1"/>
-    <col min="25" max="25" width="78.83203125" customWidth="1"/>
-    <col min="26" max="26" width="59.6640625" customWidth="1"/>
-    <col min="27" max="27" width="70" customWidth="1"/>
-    <col min="28" max="28" width="86.1640625" customWidth="1"/>
-    <col min="29" max="29" width="73" customWidth="1"/>
-    <col min="30" max="30" width="72" customWidth="1"/>
-    <col min="31" max="31" width="68.6640625" customWidth="1"/>
-    <col min="32" max="32" width="76.33203125" customWidth="1"/>
+    <col min="25" max="25" width="28.1640625" customWidth="1"/>
+    <col min="26" max="26" width="26.33203125" customWidth="1"/>
+    <col min="27" max="27" width="24" customWidth="1"/>
+    <col min="28" max="28" width="32.33203125" customWidth="1"/>
+    <col min="29" max="29" width="78.83203125" customWidth="1"/>
+    <col min="30" max="30" width="59.6640625" customWidth="1"/>
+    <col min="31" max="31" width="70" customWidth="1"/>
+    <col min="32" max="32" width="86.1640625" customWidth="1"/>
+    <col min="33" max="33" width="73" customWidth="1"/>
+    <col min="34" max="34" width="72" customWidth="1"/>
+    <col min="35" max="35" width="68.6640625" customWidth="1"/>
+    <col min="36" max="36" width="76.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="43"/>
-      <c r="B1" s="33" t="s">
+    <row r="1" spans="1:36" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="58"/>
+      <c r="B1" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="33" t="s">
+      <c r="C1" s="56"/>
+      <c r="D1" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="41" t="s">
+      <c r="E1" s="57"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="54" t="s">
         <v>182</v>
       </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41" t="s">
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="53" t="s">
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="53" t="s">
+      <c r="P1" s="39"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
-      <c r="V1" s="54"/>
-      <c r="W1" s="54"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="33" t="s">
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="Z1" s="39"/>
+      <c r="AA1" s="39"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="55" t="s">
         <v>180</v>
       </c>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="35"/>
-      <c r="AC1" s="33" t="s">
+      <c r="AD1" s="57"/>
+      <c r="AE1" s="57"/>
+      <c r="AF1" s="56"/>
+      <c r="AG1" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="34"/>
-      <c r="AF1" s="35"/>
+      <c r="AH1" s="57"/>
+      <c r="AI1" s="57"/>
+      <c r="AJ1" s="56"/>
     </row>
-    <row r="2" spans="1:32" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44"/>
+    <row r="2" spans="1:36" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="51"/>
       <c r="B2" s="14" t="s">
         <v>187</v>
       </c>
@@ -1659,10 +1730,10 @@
       <c r="N2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="66" t="s">
         <v>52</v>
       </c>
       <c r="Q2" s="15" t="s">
@@ -1681,7 +1752,7 @@
         <v>56</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="W2" s="14" t="s">
         <v>55</v>
@@ -1689,57 +1760,69 @@
       <c r="X2" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="Y2" s="23" t="s">
+      <c r="Y2" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z2" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="AA2" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="AB2" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="AC2" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="Z2" s="24" t="s">
+      <c r="AD2" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="AA2" s="24" t="s">
+      <c r="AE2" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="AB2" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC2" s="23" t="s">
+      <c r="AF2" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="AG2" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="AD2" s="24" t="s">
+      <c r="AH2" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="AE2" s="24" t="s">
+      <c r="AI2" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="AF2" s="25" t="s">
-        <v>209</v>
+      <c r="AJ2" s="26" t="s">
+        <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="42" t="s">
+    <row r="3" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="52" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="47">
+      <c r="C3" s="41">
         <v>2</v>
       </c>
-      <c r="D3" s="40">
+      <c r="D3" s="45">
         <v>2</v>
       </c>
-      <c r="E3" s="39">
+      <c r="E3" s="49">
         <v>2.0543981481481483E-2</v>
       </c>
-      <c r="F3" s="45">
+      <c r="F3" s="47">
         <v>2.4594907407407409E-2</v>
       </c>
-      <c r="G3" s="46">
+      <c r="G3" s="43">
         <v>8</v>
       </c>
-      <c r="H3" s="40">
+      <c r="H3" s="45">
         <v>0</v>
       </c>
-      <c r="I3" s="47">
+      <c r="I3" s="41">
         <v>4</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -1773,7 +1856,7 @@
         <v>62</v>
       </c>
       <c r="V3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="W3" t="s">
         <v>63</v>
@@ -1781,35 +1864,47 @@
       <c r="X3" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="37"/>
-      <c r="AB3" s="38"/>
-      <c r="AC3" s="27" t="s">
+      <c r="Y3" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="Z3" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA3" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB3" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="29"/>
+      <c r="AG3" s="59" t="s">
         <v>188</v>
       </c>
-      <c r="AD3" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="AE3" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="AF3" s="31" t="s">
-        <v>205</v>
+      <c r="AH3" s="60" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI3" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ3" s="61" t="s">
+        <v>204</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A4" s="42"/>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A4" s="52"/>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="47"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="41"/>
       <c r="J4" s="6" t="s">
         <v>6</v>
       </c>
@@ -1845,7 +1940,7 @@
         <v>67</v>
       </c>
       <c r="V4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="W4" t="s">
         <v>68</v>
@@ -1853,41 +1948,45 @@
       <c r="X4" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="37"/>
-      <c r="AA4" s="37"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="27"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="31"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="31"/>
+      <c r="AE4" s="31"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="60"/>
+      <c r="AI4" s="60"/>
+      <c r="AJ4" s="61"/>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A5" s="44" t="s">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A5" s="51" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="41">
         <v>2</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="45">
         <v>2</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="49">
         <v>1.5034722222222222E-2</v>
       </c>
-      <c r="F5" s="45">
+      <c r="F5" s="47">
         <v>1.8391203703703705E-2</v>
       </c>
-      <c r="G5" s="46">
+      <c r="G5" s="43">
         <v>6</v>
       </c>
-      <c r="H5" s="40">
+      <c r="H5" s="45">
         <v>0</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="41">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -1925,7 +2024,7 @@
         <v>70</v>
       </c>
       <c r="V5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W5" t="s">
         <v>71</v>
@@ -1933,35 +2032,47 @@
       <c r="X5" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="37"/>
-      <c r="AA5" s="37"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="27" t="s">
+      <c r="Y5" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z5" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA5" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB5" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="31"/>
+      <c r="AE5" s="31"/>
+      <c r="AF5" s="29"/>
+      <c r="AG5" s="59" t="s">
         <v>189</v>
       </c>
-      <c r="AD5" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="AE5" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="AF5" s="31" t="s">
-        <v>206</v>
+      <c r="AH5" s="60" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI5" s="60" t="s">
+        <v>199</v>
+      </c>
+      <c r="AJ5" s="61" t="s">
+        <v>205</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A6" s="44"/>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A6" s="51"/>
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="47"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="47"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="41"/>
       <c r="J6" s="6" t="s">
         <v>6</v>
       </c>
@@ -1994,7 +2105,7 @@
         <v>76</v>
       </c>
       <c r="V6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="W6" t="s">
         <v>77</v>
@@ -2002,41 +2113,45 @@
       <c r="X6" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="37"/>
-      <c r="AA6" s="37"/>
-      <c r="AB6" s="38"/>
-      <c r="AC6" s="27"/>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="31"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="31"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="31"/>
+      <c r="AE6" s="31"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="60"/>
+      <c r="AI6" s="60"/>
+      <c r="AJ6" s="61"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A7" s="42" t="s">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="41">
         <v>2</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="45">
         <v>2</v>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="49">
         <v>1.5509259259259259E-2</v>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="47">
         <v>2.0706018518518519E-2</v>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="43">
         <v>4</v>
       </c>
-      <c r="H7" s="40">
+      <c r="H7" s="45">
         <v>1</v>
       </c>
-      <c r="I7" s="47">
+      <c r="I7" s="41">
         <v>2</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -2076,7 +2191,7 @@
         <v>91</v>
       </c>
       <c r="V7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="W7" t="s">
         <v>81</v>
@@ -2084,33 +2199,45 @@
       <c r="X7" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="37"/>
-      <c r="AA7" s="37"/>
-      <c r="AB7" s="38"/>
-      <c r="AC7" s="27" t="s">
+      <c r="Y7" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z7" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA7" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB7" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC7" s="32"/>
+      <c r="AD7" s="31"/>
+      <c r="AE7" s="31"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="59" t="s">
         <v>189</v>
       </c>
-      <c r="AD7" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="AE7" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="AF7" s="31"/>
+      <c r="AH7" s="60" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI7" s="60" t="s">
+        <v>200</v>
+      </c>
+      <c r="AJ7" s="61"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A8" s="42"/>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A8" s="52"/>
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="47"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="41"/>
       <c r="J8" s="6" t="s">
         <v>6</v>
       </c>
@@ -2145,7 +2272,7 @@
         <v>84</v>
       </c>
       <c r="V8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="W8" t="s">
         <v>85</v>
@@ -2153,41 +2280,45 @@
       <c r="X8" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="37"/>
-      <c r="AB8" s="38"/>
-      <c r="AC8" s="27"/>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="29"/>
-      <c r="AF8" s="31"/>
+      <c r="Y8" s="32"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="29"/>
+      <c r="AC8" s="32"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="31"/>
+      <c r="AF8" s="29"/>
+      <c r="AG8" s="59"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="61"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A9" s="44" t="s">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A9" s="51" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="41">
         <v>2</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="45">
         <v>2</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="49">
         <v>1.846064814814815E-2</v>
       </c>
-      <c r="F9" s="45">
+      <c r="F9" s="47">
         <v>2.3530092592592592E-2</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="43">
         <v>7</v>
       </c>
-      <c r="H9" s="40">
+      <c r="H9" s="45">
         <v>0</v>
       </c>
-      <c r="I9" s="47">
+      <c r="I9" s="41">
         <v>4</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -2221,7 +2352,7 @@
         <v>92</v>
       </c>
       <c r="V9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="W9" t="s">
         <v>139</v>
@@ -2229,35 +2360,47 @@
       <c r="X9" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="37"/>
-      <c r="AB9" s="38"/>
-      <c r="AC9" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="AD9" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="AE9" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="AF9" s="31" t="s">
-        <v>207</v>
+      <c r="Y9" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z9" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA9" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB9" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC9" s="32"/>
+      <c r="AD9" s="31"/>
+      <c r="AE9" s="31"/>
+      <c r="AF9" s="29"/>
+      <c r="AG9" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="AH9" s="60" t="s">
+        <v>195</v>
+      </c>
+      <c r="AI9" s="60" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ9" s="61" t="s">
+        <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A10" s="44"/>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A10" s="51"/>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="47"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="6" t="s">
         <v>6</v>
       </c>
@@ -2289,7 +2432,7 @@
         <v>87</v>
       </c>
       <c r="V10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="W10" t="s">
         <v>88</v>
@@ -2297,41 +2440,45 @@
       <c r="X10" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="Y10" s="36"/>
-      <c r="Z10" s="37"/>
-      <c r="AA10" s="37"/>
-      <c r="AB10" s="38"/>
-      <c r="AC10" s="27"/>
-      <c r="AD10" s="29"/>
-      <c r="AE10" s="29"/>
-      <c r="AF10" s="31"/>
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="29"/>
+      <c r="AC10" s="32"/>
+      <c r="AD10" s="31"/>
+      <c r="AE10" s="31"/>
+      <c r="AF10" s="29"/>
+      <c r="AG10" s="59"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="61"/>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A11" s="42" t="s">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A11" s="52" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="41">
         <v>2</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="45">
         <v>2</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="49">
         <v>1.9629629629629629E-2</v>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="47">
         <v>2.4814814814814814E-2</v>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="43">
         <v>5</v>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="45">
         <v>1</v>
       </c>
-      <c r="I11" s="47">
+      <c r="I11" s="41">
         <v>2</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -2369,7 +2516,7 @@
         <v>96</v>
       </c>
       <c r="V11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="W11" t="s">
         <v>101</v>
@@ -2377,35 +2524,47 @@
       <c r="X11" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="Y11" s="36"/>
-      <c r="Z11" s="37"/>
-      <c r="AA11" s="37"/>
-      <c r="AB11" s="38"/>
-      <c r="AC11" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="AD11" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="AE11" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="AF11" s="31" t="s">
-        <v>207</v>
+      <c r="Y11" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="Z11" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA11" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB11" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC11" s="32"/>
+      <c r="AD11" s="31"/>
+      <c r="AE11" s="31"/>
+      <c r="AF11" s="29"/>
+      <c r="AG11" s="59" t="s">
+        <v>190</v>
+      </c>
+      <c r="AH11" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI11" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="AJ11" s="61" t="s">
+        <v>206</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="42"/>
+    <row r="12" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="52"/>
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="47"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="41"/>
       <c r="J12" s="6" t="s">
         <v>19</v>
       </c>
@@ -2440,7 +2599,7 @@
         <v>100</v>
       </c>
       <c r="V12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W12" t="s">
         <v>102</v>
@@ -2448,79 +2607,83 @@
       <c r="X12" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="Y12" s="36"/>
-      <c r="Z12" s="37"/>
-      <c r="AA12" s="37"/>
-      <c r="AB12" s="38"/>
-      <c r="AC12" s="27"/>
-      <c r="AD12" s="29"/>
-      <c r="AE12" s="29"/>
-      <c r="AF12" s="31"/>
+      <c r="Y12" s="32"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="29"/>
+      <c r="AC12" s="32"/>
+      <c r="AD12" s="31"/>
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="29"/>
+      <c r="AG12" s="59"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="61"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="65" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="8">
         <v>1</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="37"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="36" t="s">
+      <c r="E13" s="31"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="H13" s="37"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="36" t="s">
+      <c r="H13" s="31"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="37"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="38"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="29"/>
       <c r="O13" s="6"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="6"/>
       <c r="X13" s="9"/>
-      <c r="Y13" s="6"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="20"/>
-      <c r="AE13" s="20"/>
-      <c r="AF13" s="22"/>
+      <c r="AC13" s="6"/>
+      <c r="AF13" s="9"/>
+      <c r="AG13" s="22"/>
+      <c r="AH13" s="21"/>
+      <c r="AI13" s="21"/>
+      <c r="AJ13" s="23"/>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A14" s="42" t="s">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A14" s="52" t="s">
         <v>28</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="41">
         <v>2</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="45">
         <v>2</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="49">
         <v>1.7430555555555557E-2</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="47">
         <v>2.3020833333333334E-2</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="43">
         <v>7</v>
       </c>
-      <c r="H14" s="40">
+      <c r="H14" s="45">
         <v>0</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14" s="29">
         <v>1</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -2557,7 +2720,7 @@
         <v>91</v>
       </c>
       <c r="V14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="W14" t="s">
         <v>106</v>
@@ -2565,35 +2728,47 @@
       <c r="X14" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="Y14" s="36"/>
-      <c r="Z14" s="37"/>
-      <c r="AA14" s="37"/>
-      <c r="AB14" s="38"/>
-      <c r="AC14" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="AD14" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="AE14" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="AF14" s="31" t="s">
-        <v>208</v>
+      <c r="Y14" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z14" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA14" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB14" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC14" s="32"/>
+      <c r="AD14" s="31"/>
+      <c r="AE14" s="31"/>
+      <c r="AF14" s="29"/>
+      <c r="AG14" s="59" t="s">
+        <v>191</v>
+      </c>
+      <c r="AH14" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="AI14" s="60" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ14" s="61" t="s">
+        <v>207</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A15" s="42"/>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A15" s="52"/>
       <c r="B15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="38"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="29"/>
       <c r="J15" s="6" t="s">
         <v>6</v>
       </c>
@@ -2628,7 +2803,7 @@
         <v>110</v>
       </c>
       <c r="V15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W15" t="s">
         <v>112</v>
@@ -2636,20 +2811,24 @@
       <c r="X15" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="Y15" s="36"/>
-      <c r="Z15" s="37"/>
-      <c r="AA15" s="37"/>
-      <c r="AB15" s="38"/>
-      <c r="AC15" s="27"/>
-      <c r="AD15" s="29"/>
-      <c r="AE15" s="29"/>
-      <c r="AF15" s="31"/>
+      <c r="Y15" s="32"/>
+      <c r="Z15" s="31"/>
+      <c r="AA15" s="31"/>
+      <c r="AB15" s="29"/>
+      <c r="AC15" s="32"/>
+      <c r="AD15" s="31"/>
+      <c r="AE15" s="31"/>
+      <c r="AF15" s="29"/>
+      <c r="AG15" s="59"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="61"/>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="65" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="8">
@@ -2716,49 +2895,61 @@
       <c r="X16" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="Y16" t="s">
-        <v>210</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>222</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>228</v>
-      </c>
-      <c r="AC16" s="21"/>
-      <c r="AD16" s="20"/>
-      <c r="AE16" s="20"/>
-      <c r="AF16" s="22"/>
+      <c r="Y16" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z16" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA16" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB16" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>246</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>220</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>226</v>
+      </c>
+      <c r="AG16" s="22"/>
+      <c r="AH16" s="21"/>
+      <c r="AI16" s="21"/>
+      <c r="AJ16" s="23"/>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A17" s="42" t="s">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A17" s="52" t="s">
         <v>32</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="41">
         <v>2</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="45">
         <v>4</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="49">
         <v>4.5023148148148149E-3</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="47">
         <v>1.5983796296296298E-2</v>
       </c>
-      <c r="G17" s="46">
+      <c r="G17" s="43">
         <v>3</v>
       </c>
-      <c r="H17" s="40">
+      <c r="H17" s="45">
         <v>0</v>
       </c>
-      <c r="I17" s="47" t="s">
+      <c r="I17" s="41" t="s">
         <v>45</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -2798,7 +2989,7 @@
         <v>121</v>
       </c>
       <c r="V17" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="W17" t="s">
         <v>106</v>
@@ -2806,35 +2997,47 @@
       <c r="X17" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="Y17" s="27" t="s">
-        <v>211</v>
-      </c>
-      <c r="Z17" s="29" t="s">
-        <v>216</v>
-      </c>
-      <c r="AA17" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB17" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="AC17" s="27"/>
-      <c r="AD17" s="29"/>
-      <c r="AE17" s="29"/>
-      <c r="AF17" s="31"/>
+      <c r="Y17" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z17" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA17" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB17" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC17" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="AD17" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="AE17" s="60" t="s">
+        <v>221</v>
+      </c>
+      <c r="AF17" s="61" t="s">
+        <v>227</v>
+      </c>
+      <c r="AG17" s="59"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="61"/>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A18" s="42"/>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A18" s="52"/>
       <c r="B18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="47"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="41"/>
       <c r="J18" s="6" t="s">
         <v>6</v>
       </c>
@@ -2880,41 +3083,45 @@
       <c r="X18" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="Y18" s="27"/>
-      <c r="Z18" s="29"/>
-      <c r="AA18" s="29"/>
-      <c r="AB18" s="31"/>
-      <c r="AC18" s="27"/>
-      <c r="AD18" s="29"/>
-      <c r="AE18" s="29"/>
-      <c r="AF18" s="31"/>
+      <c r="Y18" s="32"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="29"/>
+      <c r="AC18" s="59"/>
+      <c r="AD18" s="60"/>
+      <c r="AE18" s="60"/>
+      <c r="AF18" s="61"/>
+      <c r="AG18" s="59"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="61"/>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A19" s="44" t="s">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A19" s="51" t="s">
         <v>33</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="47">
+      <c r="C19" s="41">
         <v>2</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="45">
         <v>4</v>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="49">
         <v>2.3726851851851851E-3</v>
       </c>
-      <c r="F19" s="45">
+      <c r="F19" s="47">
         <v>1.1203703703703704E-2</v>
       </c>
-      <c r="G19" s="46">
+      <c r="G19" s="43">
         <v>0</v>
       </c>
-      <c r="H19" s="40">
+      <c r="H19" s="45">
         <v>0</v>
       </c>
-      <c r="I19" s="47" t="s">
+      <c r="I19" s="41" t="s">
         <v>45</v>
       </c>
       <c r="J19" s="6" t="s">
@@ -2957,35 +3164,47 @@
       <c r="X19" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="Y19" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="Z19" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA19" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB19" s="31" t="s">
+      <c r="Y19" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z19" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA19" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB19" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC19" s="59" t="s">
+        <v>211</v>
+      </c>
+      <c r="AD19" s="60" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE19" s="60" t="s">
+        <v>221</v>
+      </c>
+      <c r="AF19" s="61" t="s">
         <v>179</v>
       </c>
-      <c r="AC19" s="27"/>
-      <c r="AD19" s="29"/>
-      <c r="AE19" s="29"/>
-      <c r="AF19" s="31"/>
+      <c r="AG19" s="59"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="61"/>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A20" s="44"/>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A20" s="51"/>
       <c r="B20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="47"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="41"/>
       <c r="J20" s="6" t="s">
         <v>6</v>
       </c>
@@ -3028,41 +3247,45 @@
       <c r="X20" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="29"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="31"/>
-      <c r="AC20" s="27"/>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="31"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="31"/>
+      <c r="AB20" s="29"/>
+      <c r="AC20" s="59"/>
+      <c r="AD20" s="60"/>
+      <c r="AE20" s="60"/>
+      <c r="AF20" s="61"/>
+      <c r="AG20" s="59"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="61"/>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A21" s="42" t="s">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A21" s="52" t="s">
         <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="41">
         <v>2</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="45">
         <v>4</v>
       </c>
-      <c r="E21" s="39">
+      <c r="E21" s="49">
         <v>3.2986111111111111E-3</v>
       </c>
-      <c r="F21" s="45">
+      <c r="F21" s="47">
         <v>1.6168981481481482E-2</v>
       </c>
-      <c r="G21" s="46">
+      <c r="G21" s="43">
         <v>0</v>
       </c>
-      <c r="H21" s="40">
+      <c r="H21" s="45">
         <v>0</v>
       </c>
-      <c r="I21" s="47" t="s">
+      <c r="I21" s="41" t="s">
         <v>45</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -3100,7 +3323,7 @@
         <v>138</v>
       </c>
       <c r="V21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="W21" t="s">
         <v>140</v>
@@ -3108,35 +3331,47 @@
       <c r="X21" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="Y21" s="27" t="s">
-        <v>213</v>
-      </c>
-      <c r="Z21" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="AA21" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="AB21" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="AC21" s="27"/>
-      <c r="AD21" s="29"/>
-      <c r="AE21" s="29"/>
-      <c r="AF21" s="31"/>
+      <c r="Y21" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z21" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA21" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB21" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC21" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD21" s="60" t="s">
+        <v>216</v>
+      </c>
+      <c r="AE21" s="60" t="s">
+        <v>222</v>
+      </c>
+      <c r="AF21" s="61" t="s">
+        <v>228</v>
+      </c>
+      <c r="AG21" s="59"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="61"/>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A22" s="42"/>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A22" s="52"/>
       <c r="B22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="47"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="41"/>
       <c r="J22" s="6" t="s">
         <v>6</v>
       </c>
@@ -3172,7 +3407,7 @@
         <v>144</v>
       </c>
       <c r="V22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="W22" t="s">
         <v>145</v>
@@ -3180,41 +3415,45 @@
       <c r="X22" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="Y22" s="27"/>
-      <c r="Z22" s="29"/>
-      <c r="AA22" s="29"/>
-      <c r="AB22" s="31"/>
-      <c r="AC22" s="27"/>
-      <c r="AD22" s="29"/>
-      <c r="AE22" s="29"/>
-      <c r="AF22" s="31"/>
+      <c r="Y22" s="32"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="31"/>
+      <c r="AB22" s="29"/>
+      <c r="AC22" s="59"/>
+      <c r="AD22" s="60"/>
+      <c r="AE22" s="60"/>
+      <c r="AF22" s="61"/>
+      <c r="AG22" s="59"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="61"/>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A23" s="44" t="s">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A23" s="51" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="47">
+      <c r="C23" s="41">
         <v>2</v>
       </c>
-      <c r="D23" s="40">
+      <c r="D23" s="45">
         <v>4</v>
       </c>
-      <c r="E23" s="39">
+      <c r="E23" s="49">
         <v>2.7430555555555554E-3</v>
       </c>
-      <c r="F23" s="45">
+      <c r="F23" s="47">
         <v>1.5787037037037037E-2</v>
       </c>
-      <c r="G23" s="46">
+      <c r="G23" s="43">
         <v>1</v>
       </c>
-      <c r="H23" s="40">
+      <c r="H23" s="45">
         <v>0</v>
       </c>
-      <c r="I23" s="47" t="s">
+      <c r="I23" s="41" t="s">
         <v>45</v>
       </c>
       <c r="J23" s="6" t="s">
@@ -3252,35 +3491,47 @@
         <v>150</v>
       </c>
       <c r="X23" s="9"/>
-      <c r="Y23" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z23" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="AA23" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="AB23" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="AC23" s="27"/>
-      <c r="AD23" s="29"/>
-      <c r="AE23" s="29"/>
-      <c r="AF23" s="31"/>
+      <c r="Y23" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z23" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA23" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB23" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC23" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD23" s="60" t="s">
+        <v>217</v>
+      </c>
+      <c r="AE23" s="60" t="s">
+        <v>223</v>
+      </c>
+      <c r="AF23" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="AG23" s="59"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="61"/>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A24" s="44"/>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A24" s="51"/>
       <c r="B24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="47"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="41"/>
       <c r="J24" s="6" t="s">
         <v>6</v>
       </c>
@@ -3318,41 +3569,45 @@
       <c r="X24" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="Y24" s="27"/>
-      <c r="Z24" s="29"/>
-      <c r="AA24" s="29"/>
-      <c r="AB24" s="31"/>
-      <c r="AC24" s="27"/>
-      <c r="AD24" s="29"/>
-      <c r="AE24" s="29"/>
-      <c r="AF24" s="31"/>
+      <c r="Y24" s="32"/>
+      <c r="Z24" s="31"/>
+      <c r="AA24" s="31"/>
+      <c r="AB24" s="29"/>
+      <c r="AC24" s="59"/>
+      <c r="AD24" s="60"/>
+      <c r="AE24" s="60"/>
+      <c r="AF24" s="61"/>
+      <c r="AG24" s="59"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="61"/>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A25" s="42" t="s">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A25" s="52" t="s">
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="47">
+      <c r="C25" s="41">
         <v>2</v>
       </c>
-      <c r="D25" s="40">
+      <c r="D25" s="45">
         <v>4</v>
       </c>
-      <c r="E25" s="39">
+      <c r="E25" s="49">
         <v>3.7499999999999999E-3</v>
       </c>
-      <c r="F25" s="45">
+      <c r="F25" s="47">
         <v>1.2766203703703703E-2</v>
       </c>
-      <c r="G25" s="46">
+      <c r="G25" s="43">
         <v>0</v>
       </c>
-      <c r="H25" s="40">
+      <c r="H25" s="45">
         <v>0</v>
       </c>
-      <c r="I25" s="47" t="s">
+      <c r="I25" s="41" t="s">
         <v>45</v>
       </c>
       <c r="J25" s="6" t="s">
@@ -3392,7 +3647,7 @@
         <v>154</v>
       </c>
       <c r="V25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="W25" t="s">
         <v>155</v>
@@ -3400,33 +3655,45 @@
       <c r="X25" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="Y25" s="27" t="s">
+      <c r="Y25" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z25" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA25" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB25" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC25" s="59" t="s">
         <v>181</v>
       </c>
-      <c r="Z25" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="AA25" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="AB25" s="31"/>
-      <c r="AC25" s="27"/>
-      <c r="AD25" s="29"/>
-      <c r="AE25" s="29"/>
-      <c r="AF25" s="31"/>
+      <c r="AD25" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="AE25" s="60" t="s">
+        <v>224</v>
+      </c>
+      <c r="AF25" s="61"/>
+      <c r="AG25" s="59"/>
+      <c r="AH25" s="60"/>
+      <c r="AI25" s="60"/>
+      <c r="AJ25" s="61"/>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A26" s="42"/>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A26" s="52"/>
       <c r="B26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="47"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="41"/>
       <c r="J26" s="6" t="s">
         <v>19</v>
       </c>
@@ -3464,7 +3731,7 @@
         <v>159</v>
       </c>
       <c r="V26" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="W26" t="s">
         <v>160</v>
@@ -3472,41 +3739,45 @@
       <c r="X26" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="31"/>
-      <c r="AC26" s="27"/>
-      <c r="AD26" s="29"/>
-      <c r="AE26" s="29"/>
-      <c r="AF26" s="31"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="34"/>
+      <c r="AA26" s="34"/>
+      <c r="AB26" s="37"/>
+      <c r="AC26" s="59"/>
+      <c r="AD26" s="60"/>
+      <c r="AE26" s="60"/>
+      <c r="AF26" s="61"/>
+      <c r="AG26" s="59"/>
+      <c r="AH26" s="60"/>
+      <c r="AI26" s="60"/>
+      <c r="AJ26" s="61"/>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A27" s="44" t="s">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A27" s="51" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="41">
         <v>2</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D27" s="45">
         <v>4</v>
       </c>
-      <c r="E27" s="39">
+      <c r="E27" s="49">
         <v>3.8773148148148148E-3</v>
       </c>
-      <c r="F27" s="45">
+      <c r="F27" s="47">
         <v>1.9502314814814816E-2</v>
       </c>
-      <c r="G27" s="46">
+      <c r="G27" s="43">
         <v>4</v>
       </c>
-      <c r="H27" s="40">
+      <c r="H27" s="45">
         <v>0</v>
       </c>
-      <c r="I27" s="47" t="s">
+      <c r="I27" s="41" t="s">
         <v>45</v>
       </c>
       <c r="J27" s="6" t="s">
@@ -3549,35 +3820,47 @@
       <c r="X27" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="Y27" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="Z27" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA27" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="AB27" s="31" t="s">
-        <v>232</v>
-      </c>
-      <c r="AC27" s="27"/>
-      <c r="AD27" s="29"/>
-      <c r="AE27" s="29"/>
-      <c r="AF27" s="31"/>
+      <c r="Y27" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z27" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA27" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB27" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC27" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD27" s="60" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE27" s="60" t="s">
+        <v>225</v>
+      </c>
+      <c r="AF27" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="AG27" s="59"/>
+      <c r="AH27" s="60"/>
+      <c r="AI27" s="60"/>
+      <c r="AJ27" s="61"/>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A28" s="49"/>
-      <c r="B28" s="26" t="s">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A28" s="53"/>
+      <c r="B28" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="51"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="42"/>
       <c r="J28" s="7" t="s">
         <v>6</v>
       </c>
@@ -3621,17 +3904,204 @@
       <c r="X28" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="Y28" s="28"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="32"/>
-      <c r="AC28" s="28"/>
-      <c r="AD28" s="30"/>
-      <c r="AE28" s="30"/>
-      <c r="AF28" s="32"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="36"/>
+      <c r="AA28" s="36"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="62"/>
+      <c r="AD28" s="63"/>
+      <c r="AE28" s="63"/>
+      <c r="AF28" s="64"/>
+      <c r="AG28" s="62"/>
+      <c r="AH28" s="63"/>
+      <c r="AI28" s="63"/>
+      <c r="AJ28" s="64"/>
     </row>
   </sheetData>
-  <mergeCells count="204">
+  <mergeCells count="253">
+    <mergeCell ref="AG27:AG28"/>
+    <mergeCell ref="AH27:AH28"/>
+    <mergeCell ref="AI27:AI28"/>
+    <mergeCell ref="AJ27:AJ28"/>
+    <mergeCell ref="AG21:AG22"/>
+    <mergeCell ref="AH21:AH22"/>
+    <mergeCell ref="AI21:AI22"/>
+    <mergeCell ref="AJ21:AJ22"/>
+    <mergeCell ref="AG23:AG24"/>
+    <mergeCell ref="AH23:AH24"/>
+    <mergeCell ref="AI23:AI24"/>
+    <mergeCell ref="AJ23:AJ24"/>
+    <mergeCell ref="AG25:AG26"/>
+    <mergeCell ref="AH25:AH26"/>
+    <mergeCell ref="AI25:AI26"/>
+    <mergeCell ref="AJ25:AJ26"/>
+    <mergeCell ref="AG14:AG15"/>
+    <mergeCell ref="AH14:AH15"/>
+    <mergeCell ref="AI14:AI15"/>
+    <mergeCell ref="AJ14:AJ15"/>
+    <mergeCell ref="AG17:AG18"/>
+    <mergeCell ref="AH17:AH18"/>
+    <mergeCell ref="AI17:AI18"/>
+    <mergeCell ref="AJ17:AJ18"/>
+    <mergeCell ref="AG19:AG20"/>
+    <mergeCell ref="AH19:AH20"/>
+    <mergeCell ref="AI19:AI20"/>
+    <mergeCell ref="AJ19:AJ20"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AH8"/>
+    <mergeCell ref="AI7:AI8"/>
+    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="AG9:AG10"/>
+    <mergeCell ref="AH9:AH10"/>
+    <mergeCell ref="AI9:AI10"/>
+    <mergeCell ref="AJ9:AJ10"/>
+    <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="AH11:AH12"/>
+    <mergeCell ref="AI11:AI12"/>
+    <mergeCell ref="AJ11:AJ12"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AG1:AJ1"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="AH3:AH4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AD5:AD6"/>
+    <mergeCell ref="AD7:AD8"/>
+    <mergeCell ref="AD9:AD10"/>
+    <mergeCell ref="AD11:AD12"/>
+    <mergeCell ref="AE11:AE12"/>
+    <mergeCell ref="AF11:AF12"/>
+    <mergeCell ref="AE9:AE10"/>
+    <mergeCell ref="AE7:AE8"/>
+    <mergeCell ref="AE5:AE6"/>
+    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="AF7:AF8"/>
+    <mergeCell ref="AF9:AF10"/>
+    <mergeCell ref="AC21:AC22"/>
+    <mergeCell ref="AD21:AD22"/>
+    <mergeCell ref="AE21:AE22"/>
+    <mergeCell ref="AF21:AF22"/>
+    <mergeCell ref="AC23:AC24"/>
+    <mergeCell ref="AC25:AC26"/>
+    <mergeCell ref="AC27:AC28"/>
+    <mergeCell ref="AD23:AD24"/>
+    <mergeCell ref="AD25:AD26"/>
+    <mergeCell ref="AD27:AD28"/>
+    <mergeCell ref="AE23:AE24"/>
+    <mergeCell ref="AE25:AE26"/>
+    <mergeCell ref="AE27:AE28"/>
+    <mergeCell ref="AF23:AF24"/>
+    <mergeCell ref="AF25:AF26"/>
+    <mergeCell ref="AF27:AF28"/>
+    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="AC9:AC10"/>
+    <mergeCell ref="AC7:AC8"/>
+    <mergeCell ref="AC5:AC6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="Z7:Z8"/>
+    <mergeCell ref="AA7:AA8"/>
+    <mergeCell ref="AC17:AC18"/>
+    <mergeCell ref="AD17:AD18"/>
+    <mergeCell ref="AE17:AE18"/>
+    <mergeCell ref="AF17:AF18"/>
+    <mergeCell ref="AC19:AC20"/>
+    <mergeCell ref="AD19:AD20"/>
+    <mergeCell ref="AE19:AE20"/>
+    <mergeCell ref="AF19:AF20"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AE14:AE15"/>
+    <mergeCell ref="AF14:AF15"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="E25:E26"/>
     <mergeCell ref="I25:I26"/>
     <mergeCell ref="I27:I28"/>
     <mergeCell ref="O1:Q1"/>
@@ -3656,186 +4126,52 @@
     <mergeCell ref="J13:N13"/>
     <mergeCell ref="H5:H6"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="Y17:Y18"/>
-    <mergeCell ref="Z17:Z18"/>
-    <mergeCell ref="AA17:AA18"/>
-    <mergeCell ref="AB17:AB18"/>
-    <mergeCell ref="Y19:Y20"/>
-    <mergeCell ref="Z19:Z20"/>
-    <mergeCell ref="AA19:AA20"/>
-    <mergeCell ref="AB19:AB20"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="AB7:AB8"/>
+    <mergeCell ref="Y9:Y10"/>
+    <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="AA9:AA10"/>
+    <mergeCell ref="AB9:AB10"/>
+    <mergeCell ref="AB11:AB12"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="Y14:Y15"/>
     <mergeCell ref="Z14:Z15"/>
     <mergeCell ref="AA14:AA15"/>
     <mergeCell ref="AB14:AB15"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="Y9:Y10"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="Y21:Y22"/>
-    <mergeCell ref="Z21:Z22"/>
-    <mergeCell ref="AA21:AA22"/>
+    <mergeCell ref="AB17:AB18"/>
+    <mergeCell ref="AB19:AB20"/>
     <mergeCell ref="AB21:AB22"/>
-    <mergeCell ref="Y23:Y24"/>
-    <mergeCell ref="Y25:Y26"/>
-    <mergeCell ref="Y27:Y28"/>
-    <mergeCell ref="Z23:Z24"/>
-    <mergeCell ref="Z25:Z26"/>
-    <mergeCell ref="Z27:Z28"/>
-    <mergeCell ref="AA23:AA24"/>
-    <mergeCell ref="AA25:AA26"/>
-    <mergeCell ref="AA27:AA28"/>
     <mergeCell ref="AB23:AB24"/>
     <mergeCell ref="AB25:AB26"/>
     <mergeCell ref="AB27:AB28"/>
-    <mergeCell ref="Z7:Z8"/>
-    <mergeCell ref="Z9:Z10"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="AA11:AA12"/>
-    <mergeCell ref="AB11:AB12"/>
-    <mergeCell ref="AA9:AA10"/>
-    <mergeCell ref="AA7:AA8"/>
-    <mergeCell ref="AA5:AA6"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="AB5:AB6"/>
-    <mergeCell ref="AB7:AB8"/>
-    <mergeCell ref="AB9:AB10"/>
-    <mergeCell ref="Y1:AB1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AC5:AC6"/>
-    <mergeCell ref="AD5:AD6"/>
-    <mergeCell ref="AE5:AE6"/>
-    <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="AC7:AC8"/>
-    <mergeCell ref="AD7:AD8"/>
-    <mergeCell ref="AE7:AE8"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="AC9:AC10"/>
-    <mergeCell ref="AD9:AD10"/>
-    <mergeCell ref="AE9:AE10"/>
-    <mergeCell ref="AF9:AF10"/>
-    <mergeCell ref="AC11:AC12"/>
-    <mergeCell ref="AD11:AD12"/>
-    <mergeCell ref="AE11:AE12"/>
-    <mergeCell ref="AF11:AF12"/>
-    <mergeCell ref="AC14:AC15"/>
-    <mergeCell ref="AD14:AD15"/>
-    <mergeCell ref="AE14:AE15"/>
-    <mergeCell ref="AF14:AF15"/>
-    <mergeCell ref="AC17:AC18"/>
-    <mergeCell ref="AD17:AD18"/>
-    <mergeCell ref="AE17:AE18"/>
-    <mergeCell ref="AF17:AF18"/>
-    <mergeCell ref="AC19:AC20"/>
-    <mergeCell ref="AD19:AD20"/>
-    <mergeCell ref="AE19:AE20"/>
-    <mergeCell ref="AF19:AF20"/>
-    <mergeCell ref="AC27:AC28"/>
-    <mergeCell ref="AD27:AD28"/>
-    <mergeCell ref="AE27:AE28"/>
-    <mergeCell ref="AF27:AF28"/>
-    <mergeCell ref="AC21:AC22"/>
-    <mergeCell ref="AD21:AD22"/>
-    <mergeCell ref="AE21:AE22"/>
-    <mergeCell ref="AF21:AF22"/>
-    <mergeCell ref="AC23:AC24"/>
-    <mergeCell ref="AD23:AD24"/>
-    <mergeCell ref="AE23:AE24"/>
-    <mergeCell ref="AF23:AF24"/>
-    <mergeCell ref="AC25:AC26"/>
-    <mergeCell ref="AD25:AD26"/>
-    <mergeCell ref="AE25:AE26"/>
-    <mergeCell ref="AF25:AF26"/>
+    <mergeCell ref="AA17:AA18"/>
+    <mergeCell ref="Z17:Z18"/>
+    <mergeCell ref="Y17:Y18"/>
+    <mergeCell ref="Y19:Y20"/>
+    <mergeCell ref="Z19:Z20"/>
+    <mergeCell ref="AA19:AA20"/>
+    <mergeCell ref="AA21:AA22"/>
+    <mergeCell ref="Z21:Z22"/>
+    <mergeCell ref="Y21:Y22"/>
+    <mergeCell ref="Y23:Y24"/>
+    <mergeCell ref="Z23:Z24"/>
+    <mergeCell ref="AA23:AA24"/>
+    <mergeCell ref="Y25:Y26"/>
+    <mergeCell ref="Z25:Z26"/>
+    <mergeCell ref="AA25:AA26"/>
+    <mergeCell ref="Y27:Y28"/>
+    <mergeCell ref="Z27:Z28"/>
+    <mergeCell ref="AA27:AA28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
